--- a/Employee_Reports_wi48/Piratheepan Thiyagarasa Q0601.xlsx
+++ b/Employee_Reports_wi48/Piratheepan Thiyagarasa Q0601.xlsx
@@ -548,11 +548,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -597,15 +597,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
     <col width="2" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -648,6 +648,54 @@
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ews Eq </t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>05-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>86.25%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Approved Score. date is valid</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL AVERAGE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>86.25%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
